--- a/derivatives/BAR/P4504_preprocessed.xlsx
+++ b/derivatives/BAR/P4504_preprocessed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>listno</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>trialno</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>conceptno</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>concept</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>concept_HU</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>responded</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>response_HU</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>similarity</t>
         </is>
@@ -569,7 +581,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.4815428256988525</v>
+        <v>0.4815427958965302</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +853,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.3746999204158783</v>
+        <v>0.3746999502182007</v>
       </c>
     </row>
     <row r="10">
@@ -1993,7 +2005,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.2425428926944733</v>
+        <v>0.2425429224967957</v>
       </c>
     </row>
     <row r="36">
@@ -2265,7 +2277,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.2927124202251434</v>
+        <v>0.2927124500274658</v>
       </c>
     </row>
     <row r="42">
@@ -2841,7 +2853,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.506470263004303</v>
+        <v>0.5064702033996582</v>
       </c>
     </row>
     <row r="55">
@@ -3103,7 +3115,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.5018253922462463</v>
+        <v>0.5018253326416016</v>
       </c>
     </row>
     <row r="61">
@@ -3281,7 +3293,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.6189005970954895</v>
+        <v>0.6189005374908447</v>
       </c>
     </row>
     <row r="65">
@@ -3909,7 +3921,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.4122478663921356</v>
+        <v>0.412247896194458</v>
       </c>
     </row>
     <row r="79">
@@ -4475,7 +4487,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.6612114310264587</v>
+        <v>0.6612114906311035</v>
       </c>
     </row>
     <row r="92">
@@ -4695,7 +4707,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.08255942165851593</v>
+        <v>0.08255943655967712</v>
       </c>
     </row>
     <row r="97">
